--- a/downloads/korrigierte_referenz/Schule_3NF.xlsx
+++ b/downloads/korrigierte_referenz/Schule_3NF.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER" sheetId="1" r:id="R60c6474b29754a6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KLASSE" sheetId="2" r:id="R717505abf9a9441b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNTERRICHT" sheetId="3" r:id="Re715678b45654b56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT" sheetId="4" r:id="R8d5fa63aef2d47cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER" sheetId="1" r:id="Re101855f4d1e4a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KLASSE" sheetId="2" r:id="R2cb3f24a1ebe4327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNTERRICHT" sheetId="3" r:id="Rc3e625baaee24af3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT" sheetId="4" r:id="R4765b40b5334486d"/>
   </x:sheets>
 </x:workbook>
 </file>
